--- a/PDF/data/experiencia_laboral_docente_resumida.xlsx
+++ b/PDF/data/experiencia_laboral_docente_resumida.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Bogotá, Colombia</t>
   </si>
   <si>
-    <t xml:space="preserve">Profesora Asociada</t>
+    <t xml:space="preserve">Profesora Asociada, Facultad de Psicología y Centro de Diversidad, Equidad e Inclusión</t>
   </si>
   <si>
     <t xml:space="preserve">Posdoctorado</t>
@@ -498,7 +498,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E1048576"/>
-  <sheetFormatPr defaultColWidth="8.890625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="87.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.67"/>
